--- a/01_Testes_Manuais/Projeto_Udemy/3_Bug_Reportados_Udemy_v1.0.xlsx
+++ b/01_Testes_Manuais/Projeto_Udemy/3_Bug_Reportados_Udemy_v1.0.xlsx
@@ -5,51 +5,39 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pamella Moraes\Documents\Projetos Git\QA-Projects\01_Testes_Manuais\Projeto_Udemy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pamella Moraes\Documents\QA\001. ESTUDOS ANALISTA DE TESTE QA JR\001.Exercicios\001_Udemy\Documentação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82DE94F3-E0EF-479E-90E3-090DA59A006E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE19F26C-A62A-4E24-B4FF-A028B03C39BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11040" tabRatio="245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bugs Reportados" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bugs Reportados'!$A$1:$M$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bugs Reportados'!$B$1:$L$7</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="76">
   <si>
     <t>Prioridade</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
     <t>Ambiente de Teste</t>
   </si>
   <si>
     <t>Resultado Esperado</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Low</t>
   </si>
   <si>
     <t>CT010 - Nova Busca com Filtro Ativo.mp4
 CT010 - Nova Busca com Filtro Ativo.png</t>
   </si>
   <si>
-    <t>Medium</t>
-  </si>
-  <si>
     <t>CT.07 - [Filtros] - Validar segmentação por nível Iniciante.mp4
 CT.07 - [Filtros] - Validar segmentação por nível Iniciante.png</t>
   </si>
@@ -85,12 +73,6 @@
   </si>
   <si>
     <t>BUG - [Frontend] Erro 404 na Busca: Sistema envia parâmetro "undefined" na URL</t>
-  </si>
-  <si>
-    <t>BUG - Report</t>
-  </si>
-  <si>
-    <t>Highest</t>
   </si>
   <si>
     <t>Ao tentar realizar uma busca vazia, o sistema monta a URL incorretamente inserindo a string "undefined", gerando erro 404.</t>
@@ -138,9 +120,6 @@
   </si>
   <si>
     <t>Bug - [Busca] Quebra de Relevância: Termo "Excel" retorna conteúdo não relacionado.</t>
-  </si>
-  <si>
-    <t>Média (Afeta a qualidade da busca, mas não bloqueia o uso).</t>
   </si>
   <si>
     <t>Ao realizar uma busca específica pela palavra-chave "Excel" e aplicar filtros de refinamento (Gratuito + Iniciante + Alta Avaliação), o sistema apresenta nos resultados um curso de idioma/caligrafia árabe. Isso caracteriza uma falha na precisão do motor de busca, entregando conteúdo sem relação semântica ou contextual com o termo pesquisado.</t>
@@ -168,9 +147,6 @@
   </si>
   <si>
     <t>Bug - [Busca] - Falha Crítica de Relevância e Persistência de Filtro Pós-Remoção.</t>
-  </si>
-  <si>
-    <t>Alta (A busca perde o propósito e os filtros travam).</t>
   </si>
   <si>
     <t>Ao realizar uma busca pela palavra-chave *"Excel"* e navegar até a página 3 com os filtros *Gratuito + Classificação 4.5+* ativos, o sistema apresenta cursos de caligrafia árabe e renda fixa, ignorando o termo de busca original. Adicionalmente, ao tentar remover o filtro de classificação no final da execução, o sistema retira a tag visual e atualiza a URL, mas falha em atualizar os resultados, mantendo a lista de cursos idêntica à anterior.</t>
@@ -199,9 +175,6 @@
     <t>Bug - [Busca/Filtros] - Perda de persistência do filtro de preço ao alterar o termo de pesquisa na barra superior.</t>
   </si>
   <si>
-    <t>Média (Afeta diretamente a jornada de compra e filtragem do usuário).</t>
-  </si>
-  <si>
     <t>CT.10</t>
   </si>
   <si>
@@ -228,9 +201,6 @@
     <t>Bug - [Busca/UX] - Inexistência de estado "Zero Resultados".</t>
   </si>
   <si>
-    <t>*Média* (Afeta a qualidade e a precisão do motor de busca).</t>
-  </si>
-  <si>
     <t>CT.11</t>
   </si>
   <si>
@@ -302,12 +272,48 @@
     <t>CT05_CT.05 – [Filtros] – Validar exclusão de cursos gratuitos ao filtrar por Preço (Pago).mp4
 CT05_CT.05 – [Filtros] – Validar exclusão de cursos gratuitos ao filtrar por Preço (Pago).png</t>
   </si>
+  <si>
+    <t>Alta (Porque o sistema quebrou e mostrou uma tela de erro em vez de só avisar o usuário que não podia pesquisar vazio.)</t>
+  </si>
+  <si>
+    <t>Alta (Porque pesquisar é a coisa mais importante do site, e dar erro logo na cara assusta quem quer achar um curso.)</t>
+  </si>
+  <si>
+    <t>Média (Porque dá um erro nos bastidores que faz a pesquisa perder o sentido, mas o site todo não cai, dá para continuar navegando.)</t>
+  </si>
+  <si>
+    <t>Baixa (Porque é muito difícil alguém ir clicando até a página 220 de resultados na vida real, então poucos usuários vão ver isso.)</t>
+  </si>
+  <si>
+    <t>Média (Porque o site continua funcionando normal, mas a inteligência da busca está falhando ao trazer coisas muito erradas.)</t>
+  </si>
+  <si>
+    <t>Alta (Porque a tela mente para o usuário, mostrando que tirou o filtro, mas não tira de verdade, travando os resultados antigos.)</t>
+  </si>
+  <si>
+    <t>Média (Porque quem usa bastante os filtros vai ficar confuso achando que está vendo cursos novos, e vai ter que atualizar a página na mão.)</t>
+  </si>
+  <si>
+    <t>Baixa (Porque não é um erro grave do sistema, é só o jeito que o site lida com buscas novas que é um pouco chato para quem usa.)</t>
+  </si>
+  <si>
+    <t>Baixa (Porque dá para usar o site tranquilo, é só o usuário marcar o filtro de novo se quiser. Não impede ninguém de comprar curso.)</t>
+  </si>
+  <si>
+    <t>Baixa (Porque não é um defeito no código. O site foi feito para preferir empurrar qualquer curso em vez de falar que não achou.)</t>
+  </si>
+  <si>
+    <t>Baixa (Porque a empresa quer vender, então exibir qualquer curso é até uma estratégia deles. Eles não vão querer mudar isso com urgência.)</t>
+  </si>
+  <si>
+    <t>Alta (Porque pode atrapalhar o aluno a achar o curso certo e a plataforma pode acabar perdendo algumas vendas por causa da confusão.)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -324,6 +330,11 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -385,7 +396,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -400,6 +411,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -704,299 +727,278 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="60" customWidth="1"/>
-    <col min="8" max="8" width="18.85546875" customWidth="1"/>
-    <col min="9" max="9" width="25.5703125" customWidth="1"/>
-    <col min="10" max="10" width="42.85546875" customWidth="1"/>
-    <col min="11" max="12" width="40" customWidth="1"/>
-    <col min="13" max="13" width="50" customWidth="1"/>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" customWidth="1"/>
+    <col min="6" max="6" width="60" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" customWidth="1"/>
+    <col min="8" max="8" width="25.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.140625" customWidth="1"/>
+    <col min="10" max="11" width="40" customWidth="1"/>
+    <col min="12" max="12" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="H1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:12" ht="306" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="C2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="L2" s="3"/>
+    </row>
+    <row r="3" spans="1:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" ht="306" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="4"/>
+    </row>
+    <row r="5" spans="1:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L5" s="3"/>
+    </row>
+    <row r="6" spans="1:12" ht="408" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="L6" s="5"/>
     </row>
-    <row r="2" spans="1:13" ht="306" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="L2" s="3" t="s">
+    <row r="7" spans="1:12" ht="357" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="M2" s="3"/>
-    </row>
-    <row r="3" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" spans="1:13" ht="293.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="M4" s="4"/>
-    </row>
-    <row r="5" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="M5" s="3"/>
-    </row>
-    <row r="6" spans="1:13" ht="395.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="E7" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="G7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="H7" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="I7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="M6" s="5"/>
-    </row>
-    <row r="7" spans="1:13" ht="357" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H7" s="4" t="s">
+      <c r="J7" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="J7" s="4" t="s">
+      <c r="K7" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="K7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="M7" s="4"/>
+      <c r="L7" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M7" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="B1:L7" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>